--- a/infosource_institutions_en_fr.xlsx
+++ b/infosource_institutions_en_fr.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z205"/>
+  <dimension ref="A1:Z186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,14 +1471,24 @@
           <t>RCAANC</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Crown Indigenous and Northern Affairs Canada</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Relations Couronne-Autochtones et Affaires du Nord Canada</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>https://www.rcaanc-cirnac.gc.ca/eng/1638307261809/1638307285229</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>404</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>https://www.rcaanc-cirnac.gc.ca/fra/1638307261809/1638307285229</t>
@@ -1518,7 +1528,11 @@
           <t>IAN00</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
@@ -1531,7 +1545,11 @@
           <t>gc:2230</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>https://rcaanc-cirnac.gc.ca/1638307261809/1638307285229</t>
+        </is>
+      </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>https://rcaanc-cirnac.gc.ca/1638307261809/1638307285229</t>
@@ -5028,14 +5046,22 @@
           <t>National Film Board of Canada</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Office national du film du Canada</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>http://onf-nfb.gc.ca/en/about-the-nfb/publications/info-source/</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>http://onf-nfb.gc.ca/fr/a-propos-de-lonf/publications/info-source/</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
@@ -5074,7 +5100,11 @@
         </is>
       </c>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
@@ -5086,7 +5116,11 @@
           <t>https://onf-nfb.gc.ca/about-the-nfb/publications/info-source</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>https://onf-nfb.gc.ca/a-propos-de-lonf/publications/info-source</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5776,7 +5810,11 @@
           <t>Office of the Correctional Investigator</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bureau de l’enquêteur correctionnel</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>http://www.oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-1-eng.aspx</t>
@@ -5785,8 +5823,14 @@
       <c r="J49" t="n">
         <v>404</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>http://www.oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-1-fra.aspx</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>404</v>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>www.oci-bec.gc.ca</t>
@@ -5820,7 +5864,11 @@
       <c r="U49" t="n">
         <v>0.9014</v>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
@@ -5832,7 +5880,11 @@
           <t>https://oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-1-eng.aspx</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>https://oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-1-fra.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -8634,7 +8686,11 @@
           <t>Canada Energy Regulator</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Office national de l’énergie</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>https://www.cer-rec.gc.ca/en/about/open-government/transparency/completed-access-information-requests/info-source.html</t>
@@ -8643,8 +8699,14 @@
       <c r="J75" t="n">
         <v>200</v>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://www.cer-rec.gc.ca/fr/regie/gouvernement-ouvert/transparence/demandes-acces-information-completees/info-source.html</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>200</v>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>https://www.cer-rec.gc.ca/index-eng.html</t>
@@ -8682,7 +8744,11 @@
         </is>
       </c>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr">
         <is>
@@ -8694,7 +8760,11 @@
           <t>https://cer-rec.gc.ca/about/open-government/transparency/completed-access-information-requests/info-source.html</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>https://cer-rec.gc.ca/regie/gouvernement-ouvert/transparence/demandes-acces-information-completees/info-source.html</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8948,7 +9018,11 @@
           <t>Parks Canada Agency</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Agence Parcs Canada</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>http://www.pc.gc.ca/en/agence-agency/dp-pd/infosource</t>
@@ -8957,8 +9031,14 @@
       <c r="J78" t="n">
         <v>200</v>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>http://www.pc.gc.ca/fr/agence-agency/dp-pd/infosource</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>200</v>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>www.pc.gc.ca</t>
@@ -8996,7 +9076,11 @@
         </is>
       </c>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr">
         <is>
@@ -9008,7 +9092,11 @@
           <t>https://pc.gc.ca/agence-agency/dp-pd/infosource</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>https://pc.gc.ca/agence-agency/dp-pd/infosource</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9646,14 +9734,22 @@
           <t>Sustainable Development Technology Canada</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Technologies du développement durable du Canada</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>https://www.sdtc.ca/en/about/accountability/info-source/</t>
         </is>
       </c>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://www.sdtc.ca/fr/a-propos/responsabilite/info-source/</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
@@ -9678,7 +9774,11 @@
         </is>
       </c>
       <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr">
         <is>
@@ -9690,7 +9790,11 @@
           <t>https://sdtc.ca/about/accountability/info-source</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>https://sdtc.ca/a-propos/responsabilite/info-source</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9814,7 +9918,11 @@
           <t>Canada-Nova Scotia Offshore Petroleum Board</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Office Canada – Nouvelle-Écosse des hydrocarbures extracôtiers</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>https://www.cnsopb.ns.ca/sites/default/files/resource/infosource_self_publishing_eng.pdf</t>
@@ -9823,8 +9931,14 @@
       <c r="J87" t="n">
         <v>404</v>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://www.ocnehe.ca/sites/default/files/resource/infosource_self_publishing_french.pdf</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>200</v>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>www.cnsopb.ns.ca</t>
@@ -9852,7 +9966,11 @@
         </is>
       </c>
       <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr">
         <is>
@@ -9864,7 +9982,11 @@
           <t>https://cnsopb.ns.ca/sites/default/files/resource/infosource_self_publishing_eng.pdf</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>https://ocnehe.ca/sites/default/files/resource/infosource_self_publishing_french.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11580,7 +11702,11 @@
           <t>National Security Intelligence Review Agency</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Comité de surveillance des activités de renseignement de sécurité</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
           <t>http://www.sirc-csars.gc.ca/prddpr/index-eng.html</t>
@@ -11589,8 +11715,14 @@
       <c r="J107" t="n">
         <v>200</v>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>http://www.sirc-csars.gc.ca/prddpr/index-fra.html</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>200</v>
+      </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr">
@@ -11610,7 +11742,11 @@
         </is>
       </c>
       <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr">
         <is>
@@ -11622,7 +11758,11 @@
           <t>https://sirc-csars.gc.ca/prddpr/index-eng.html</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>https://sirc-csars.gc.ca/prddpr/index-fra.html</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12470,7 +12610,11 @@
           <t>National Arts Centre</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Centre national des Arts</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr">
         <is>
           <t>http://nac-cna.ca/en/legal/infosource</t>
@@ -12479,8 +12623,14 @@
       <c r="J117" t="n">
         <v>200</v>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>http://nac-cna.ca/fr/legal/infosource</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>200</v>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>www.nac-cna.ca</t>
@@ -12508,7 +12658,11 @@
         </is>
       </c>
       <c r="U117" t="inlineStr"/>
-      <c r="V117" t="inlineStr"/>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr">
         <is>
@@ -12520,7 +12674,11 @@
           <t>https://nac-cna.ca/legal/infosource</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>https://nac-cna.ca/legal/infosource</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14250,7 +14408,11 @@
           <t>Defence Construction Canada</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Construction de Défense Canada</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t>https://www.dcc-cdc.gc.ca/documents/reports/Info_Source_E.pdf</t>
@@ -14259,8 +14421,14 @@
       <c r="J137" t="n">
         <v>200</v>
       </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://www.dcc-cdc.gc.ca/documents/reports/Info_Source_F.pdf</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>200</v>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>https://www.dcc-cdc.gc.ca/</t>
@@ -14288,7 +14456,11 @@
         </is>
       </c>
       <c r="U137" t="inlineStr"/>
-      <c r="V137" t="inlineStr"/>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr">
         <is>
@@ -14300,7 +14472,11 @@
           <t>https://dcc-cdc.gc.ca/documents/reports/Info_Source_E.pdf</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>https://dcc-cdc.gc.ca/documents/reports/Info_Source_F.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15446,17 +15622,27 @@
           <t>British Columbia Treaty Commission</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Commission des traités de la Colombie Britannique</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr">
         <is>
           <t>https://www.canada.ca/en/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/british-columbia-treaty-commission.html</t>
         </is>
       </c>
       <c r="J151" t="n">
-        <v>404</v>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/commission-traites-colombie-britannique.html</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>200</v>
+      </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
@@ -15472,11 +15658,15 @@
         </is>
       </c>
       <c r="U151" t="inlineStr"/>
-      <c r="V151" t="inlineStr"/>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W151" t="inlineStr"/>
       <c r="X151" t="inlineStr">
         <is>
-          <t>url:https://canada.ca/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/british-columbia-treaty-commission.html</t>
+          <t>manual:bc_treaty</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
@@ -15484,7 +15674,11 @@
           <t>https://canada.ca/treasury-board-secretariat/services/access-information-privacy/access-information/information-about-programs-information-holdings/british-columbia-treaty-commission.html</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr"/>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/commission-traites-colombie-britannique.html</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -15500,7 +15694,11 @@
           <t>Canada Eldor Inc.</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Canada Eldor Inc.</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr">
         <is>
           <t>https://www.cdev.gc.ca/info-source/canada-eldor-inc/</t>
@@ -15509,8 +15707,14 @@
       <c r="J152" t="n">
         <v>200</v>
       </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://www.cdev.gc.ca/fr/info-source-2/canada-eldor-inc/</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>200</v>
+      </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
@@ -15526,11 +15730,15 @@
         </is>
       </c>
       <c r="U152" t="inlineStr"/>
-      <c r="V152" t="inlineStr"/>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W152" t="inlineStr"/>
       <c r="X152" t="inlineStr">
         <is>
-          <t>url:https://cdev.gc.ca/info-source/canada-eldor-inc</t>
+          <t>manual:cdev_eldor</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -15538,7 +15746,11 @@
           <t>https://cdev.gc.ca/info-source/canada-eldor-inc</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr"/>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>https://cdev.gc.ca/info-source-2/canada-eldor-inc</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -15554,7 +15766,11 @@
           <t>Canada Hibernia Holding Corporation</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Société de gestion Canada Hibernia</t>
+        </is>
+      </c>
       <c r="I153" t="inlineStr">
         <is>
           <t>https://www.cdev.gc.ca/info-source/canada-hibernia-holding-corporation/</t>
@@ -15563,8 +15779,14 @@
       <c r="J153" t="n">
         <v>200</v>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://www.cdev.gc.ca/fr/info-source-2/societe-de-gestion-canada-hibernia/</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>200</v>
+      </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
@@ -15580,11 +15802,15 @@
         </is>
       </c>
       <c r="U153" t="inlineStr"/>
-      <c r="V153" t="inlineStr"/>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W153" t="inlineStr"/>
       <c r="X153" t="inlineStr">
         <is>
-          <t>url:https://cdev.gc.ca/info-source/canada-hibernia-holding-corporation</t>
+          <t>manual:cdev_hibernia</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -15592,7 +15818,11 @@
           <t>https://cdev.gc.ca/info-source/canada-hibernia-holding-corporation</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr"/>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>https://cdev.gc.ca/info-source-2/societe-de-gestion-canada-hibernia</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -15608,7 +15838,11 @@
           <t>Canada Post</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Postes Canada</t>
+        </is>
+      </c>
       <c r="I154" t="inlineStr">
         <is>
           <t>https://www.canadapost.ca/cpc/en/our-company/about-us/transparency-and-trust/access-to-information.page</t>
@@ -15617,8 +15851,14 @@
       <c r="J154" t="n">
         <v>200</v>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://www.canadapost-postescanada.ca/scp/fr/notre-entreprise/a-notre-sujet/transparence-et-confiance/centre-de-protection-de-la-vie-privee/info-source/introduction-a-info-source.page</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>200</v>
+      </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
@@ -15634,11 +15874,15 @@
         </is>
       </c>
       <c r="U154" t="inlineStr"/>
-      <c r="V154" t="inlineStr"/>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W154" t="inlineStr"/>
       <c r="X154" t="inlineStr">
         <is>
-          <t>url:https://canadapost.ca/cpc/our-company/about-us/transparency-and-trust/access-to-information.page</t>
+          <t>manual:canada_post</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -15646,7 +15890,11 @@
           <t>https://canadapost.ca/cpc/our-company/about-us/transparency-and-trust/access-to-information.page</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr"/>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>https://canadapost-postescanada.ca/scp/notre-entreprise/a-notre-sujet/transparence-et-confiance/centre-de-protection-de-la-vie-privee/info-source/introduction-a-info-source.page</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -15731,20 +15979,30 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Crown Indigenous and Northern Affairs Canada</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr"/>
+          <t>Federal Public Service Health Care Plan Administration Authority</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Administration du Régime de soins de santé de la fonction publique fédérale</t>
+        </is>
+      </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://www.rcaanc-cirnac.gc.ca/eng/1638307261809/1638307285229</t>
+          <t>http://www.pshcp.ca/about-the-pshcp/atip/infosourceen.aspx</t>
         </is>
       </c>
       <c r="J156" t="n">
-        <v>404</v>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://www.rssfp.ca/a-propos-du-rssfp/aiprp/infosourcefr/</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>200</v>
+      </c>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
@@ -15760,19 +16018,27 @@
         </is>
       </c>
       <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W156" t="inlineStr"/>
       <c r="X156" t="inlineStr">
         <is>
-          <t>url:https://rcaanc-cirnac.gc.ca/1638307261809/1638307285229</t>
+          <t>url:https://rssfp.ca/a-propos-du-rssfp/aiprp/infosourcefr</t>
         </is>
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>https://rcaanc-cirnac.gc.ca/1638307261809/1638307285229</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr"/>
+          <t>https://pshcp.ca/about-the-pshcp/atip/infosourceen.aspx</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>https://rssfp.ca/a-propos-du-rssfp/aiprp/infosourcefr</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -15785,30 +16051,20 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Federal Public Service Health Care Plan Administration Authority</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Administration du Régime de soins de santé de la fonction publique fédérale</t>
-        </is>
-      </c>
+          <t>Fund for Railway Accidents Involving Designated Goods</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
-          <t>http://www.pshcp.ca/about-the-pshcp/atip/infosourceen.aspx</t>
+          <t>https://fraidg.gc.ca/en/info-source-2/</t>
         </is>
       </c>
       <c r="J157" t="n">
         <v>200</v>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>https://www.rssfp.ca/a-propos-du-rssfp/aiprp/infosourcefr/</t>
-        </is>
-      </c>
-      <c r="L157" t="n">
-        <v>200</v>
-      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
@@ -15824,27 +16080,19 @@
         </is>
       </c>
       <c r="U157" t="inlineStr"/>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
+      <c r="V157" t="inlineStr"/>
       <c r="W157" t="inlineStr"/>
       <c r="X157" t="inlineStr">
         <is>
-          <t>url:https://rssfp.ca/a-propos-du-rssfp/aiprp/infosourcefr</t>
+          <t>url:https://fraidg.gc.ca/info-source-2</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>https://pshcp.ca/about-the-pshcp/atip/infosourceen.aspx</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>https://rssfp.ca/a-propos-du-rssfp/aiprp/infosourcefr</t>
-        </is>
-      </c>
+          <t>https://fraidg.gc.ca/info-source-2</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -15857,20 +16105,30 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Fund for Railway Accidents Involving Designated Goods</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
+          <t>Gwich'in Land and Water Board</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Office Gwich’in des terres et des eaux</t>
+        </is>
+      </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://fraidg.gc.ca/en/info-source-2/</t>
+          <t>https://glwb.com/our-board/access-information-requests-2</t>
         </is>
       </c>
       <c r="J158" t="n">
-        <v>200</v>
-      </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
+        <v>429</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-terres-eaux.html</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>200</v>
+      </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
@@ -15886,19 +16144,27 @@
         </is>
       </c>
       <c r="U158" t="inlineStr"/>
-      <c r="V158" t="inlineStr"/>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr">
         <is>
-          <t>url:https://fraidg.gc.ca/info-source-2</t>
+          <t>manual:gwichin_lwb</t>
         </is>
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>https://fraidg.gc.ca/info-source-2</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr"/>
+          <t>https://glwb.com/our-board/access-information-requests-2</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-terres-eaux.html</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -15911,20 +16177,30 @@
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Gwich'in Land and Water Board</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr"/>
+          <t>Infrastructure Canada</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Infrastructure Canada</t>
+        </is>
+      </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://glwb.com/our-board/access-information-requests-2</t>
+          <t>https://www.infrastructure.gc.ca/infosource/infosource-eng.html</t>
         </is>
       </c>
       <c r="J159" t="n">
-        <v>429</v>
-      </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://www.infrastructure.gc.ca/infosource/infosource-fra.html</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>200</v>
+      </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
@@ -15940,19 +16216,27 @@
         </is>
       </c>
       <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
-          <t>url:https://glwb.com/our-board/access-information-requests-2</t>
+          <t>manual:infrastructure</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>https://glwb.com/our-board/access-information-requests-2</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr"/>
+          <t>https://infrastructure.gc.ca/infosource/infosource-eng.html</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>https://infrastructure.gc.ca/infosource/infosource-fra.html</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -15965,20 +16249,30 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Infrastructure Canada</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
+          <t>Mackenzie Valley Environmental Impact Review Board</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Office d’examen des répercussions environnementales de la vallée du Mackenzie</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://www.infrastructure.gc.ca/infosource/infosource-eng.html</t>
+          <t>http://reviewboard.ca/about/access_information_requests.php</t>
         </is>
       </c>
       <c r="J160" t="n">
-        <v>200</v>
-      </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
+        <v>429</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>http://www.reviewboard.ca/about/access_information_requests.php</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>429</v>
+      </c>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
@@ -15994,19 +16288,27 @@
         </is>
       </c>
       <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W160" t="inlineStr"/>
       <c r="X160" t="inlineStr">
         <is>
-          <t>url:https://infrastructure.gc.ca/infosource/infosource-eng.html</t>
+          <t>url:https://reviewboard.ca/about/access_information_requests.php</t>
         </is>
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>https://infrastructure.gc.ca/infosource/infosource-eng.html</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr"/>
+          <t>https://reviewboard.ca/about/access_information_requests.php</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>https://reviewboard.ca/about/access_information_requests.php</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
@@ -16019,30 +16321,20 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Mackenzie Valley Environmental Impact Review Board</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Office d’examen des répercussions environnementales de la vallée du Mackenzie</t>
-        </is>
-      </c>
+          <t>Mackenzie Valley Land and Water Board</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
-          <t>http://reviewboard.ca/about/access_information_requests.php</t>
+          <t>https://mvlwb.com/our-board/access-information-requests</t>
         </is>
       </c>
       <c r="J161" t="n">
         <v>429</v>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>http://www.reviewboard.ca/about/access_information_requests.php</t>
-        </is>
-      </c>
-      <c r="L161" t="n">
-        <v>429</v>
-      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
@@ -16058,27 +16350,19 @@
         </is>
       </c>
       <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
+      <c r="V161" t="inlineStr"/>
       <c r="W161" t="inlineStr"/>
       <c r="X161" t="inlineStr">
         <is>
-          <t>url:https://reviewboard.ca/about/access_information_requests.php</t>
+          <t>url:https://mvlwb.com/our-board/access-information-requests</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>https://reviewboard.ca/about/access_information_requests.php</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>https://reviewboard.ca/about/access_information_requests.php</t>
-        </is>
-      </c>
+          <t>https://mvlwb.com/our-board/access-information-requests</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -16091,20 +16375,30 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Mackenzie Valley Land and Water Board</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
+          <t>Nunavut Water Board</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Office des eaux du Nunavut</t>
+        </is>
+      </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://mvlwb.com/our-board/access-information-requests</t>
+          <t>https://www.nwb-oen.ca/content/info-source-annual-report-2013-2014</t>
         </is>
       </c>
       <c r="J162" t="n">
-        <v>429</v>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
+        <v>200</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>http://www.nwb-oen.ca/fr/content/transparence</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>200</v>
+      </c>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
@@ -16120,19 +16414,27 @@
         </is>
       </c>
       <c r="U162" t="inlineStr"/>
-      <c r="V162" t="inlineStr"/>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W162" t="inlineStr"/>
       <c r="X162" t="inlineStr">
         <is>
-          <t>url:https://mvlwb.com/our-board/access-information-requests</t>
+          <t>manual:nunavut_water</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>https://mvlwb.com/our-board/access-information-requests</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr"/>
+          <t>https://nwb-oen.ca/content/info-source-annual-report-2013-2014</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>https://nwb-oen.ca/content/transparence</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -16145,18 +16447,16 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nunavut Water Board</t>
+          <t>Office of the Ombudsman, National Defence and Canadian Forces</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://www.nwb-oen.ca/content/info-source-annual-report-2013-2014</t>
-        </is>
-      </c>
-      <c r="J163" t="n">
-        <v>200</v>
-      </c>
+          <t>https://www.ombudsman.forces.gc.ca/en/ombudsman-ati/info-source.page</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
@@ -16178,12 +16478,12 @@
       <c r="W163" t="inlineStr"/>
       <c r="X163" t="inlineStr">
         <is>
-          <t>url:https://nwb-oen.ca/content/info-source-annual-report-2013-2014</t>
+          <t>url:https://ombudsman.forces.gc.ca/ombudsman-ati/info-source.page</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>https://nwb-oen.ca/content/info-source-annual-report-2013-2014</t>
+          <t>https://ombudsman.forces.gc.ca/ombudsman-ati/info-source.page</t>
         </is>
       </c>
       <c r="Z163" t="inlineStr"/>
@@ -16199,18 +16499,30 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Office of the Ombudsman, National Defence and Canadian Forces</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr"/>
+          <t>Port of Vancouver</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Port de Vancouver</t>
+        </is>
+      </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://www.ombudsman.forces.gc.ca/en/ombudsman-ati/info-source.page</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
+          <t>https://www.portvancouver.com/transparency/info-source/</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>403</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://view.officeapps.live.com/op/view.aspx?src=https%3A%2F%2Fwww.portvancouver.com%2Fwp-content%2Fuploads%2F2015%2F07%2F2017-Sources-de-renseignements-du-gouvernement-f%25C3%25A9d%25C3%25A9ral.docx&amp;wdOrigin=BROWSELINK</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>200</v>
+      </c>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
@@ -16226,19 +16538,27 @@
         </is>
       </c>
       <c r="U164" t="inlineStr"/>
-      <c r="V164" t="inlineStr"/>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W164" t="inlineStr"/>
       <c r="X164" t="inlineStr">
         <is>
-          <t>url:https://ombudsman.forces.gc.ca/ombudsman-ati/info-source.page</t>
+          <t>manual:port_vancouver</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>https://ombudsman.forces.gc.ca/ombudsman-ati/info-source.page</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr"/>
+          <t>https://portvancouver.com/transparency/info-source</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>https://view.officeapps.live.com/op/view.aspx?src=https%3A%2F%2Fwww.portvancouver.com%2Fwp-content%2Fuploads%2F2015%2F07%2F2017-Sources-de-renseignements-du-gouvernement-f%25C3%25A9d%25C3%25A9ral.docx&amp;wdOrigin=BROWSELINK</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -16251,17 +16571,17 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Port of Vancouver</t>
+          <t>Sahtu Land Use Planning Board</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://www.portvancouver.com/transparency/info-source/</t>
+          <t>https://slwb.com/our-board/access-information-requests-0</t>
         </is>
       </c>
       <c r="J165" t="n">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
@@ -16284,12 +16604,12 @@
       <c r="W165" t="inlineStr"/>
       <c r="X165" t="inlineStr">
         <is>
-          <t>url:https://portvancouver.com/transparency/info-source</t>
+          <t>url:https://slwb.com/our-board/access-information-requests-0</t>
         </is>
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>https://portvancouver.com/transparency/info-source</t>
+          <t>https://slwb.com/our-board/access-information-requests-0</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr"/>
@@ -16308,7 +16628,11 @@
           <t>Sahtu Land and Water Board</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr"/>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Office des terres et des eaux du Sahtu</t>
+        </is>
+      </c>
       <c r="I166" t="inlineStr">
         <is>
           <t>https://slwb.com/our-board/access-information-requests-0</t>
@@ -16317,8 +16641,14 @@
       <c r="J166" t="n">
         <v>429</v>
       </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf?_gl=1*1qsdw3z*_ga*ODE3NjYzOTEwLjE2NjYyMDQwNTQ.*_ga_1YN4RQ50MS*MTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..*_ga_DM4CTC801Y*MTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..*_ga_WH73GNZLKK*MTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..*_ga_FFVRERZXBW*MTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>429</v>
+      </c>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
@@ -16334,11 +16664,15 @@
         </is>
       </c>
       <c r="U166" t="inlineStr"/>
-      <c r="V166" t="inlineStr"/>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W166" t="inlineStr"/>
       <c r="X166" t="inlineStr">
         <is>
-          <t>url:https://slwb.com/our-board/access-information-requests-0</t>
+          <t>manual:sahtu_lwb</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
@@ -16346,7 +16680,11 @@
           <t>https://slwb.com/our-board/access-information-requests-0</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr"/>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf?_gl=1%2A1qsdw3z%2A_ga%2AODE3NjYzOTEwLjE2NjYyMDQwNTQ.%2A_ga_1YN4RQ50MS%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_DM4CTC801Y%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_WH73GNZLKK%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_FFVRERZXBW%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -16362,7 +16700,11 @@
           <t>Seaway International Bridge Corporation Limited</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Corporation du Pont international de la Voie maritime, Limitée</t>
+        </is>
+      </c>
       <c r="I167" t="inlineStr">
         <is>
           <t>https://www.federalbridge.ca/transparency/info-source-sources-of-federal-government-and-employee-information/</t>
@@ -16371,8 +16713,14 @@
       <c r="J167" t="n">
         <v>200</v>
       </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://www.pontsfederaux.ca/sources/cpivm/</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>200</v>
+      </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
@@ -16388,11 +16736,15 @@
         </is>
       </c>
       <c r="U167" t="inlineStr"/>
-      <c r="V167" t="inlineStr"/>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W167" t="inlineStr"/>
       <c r="X167" t="inlineStr">
         <is>
-          <t>url:https://federalbridge.ca/transparency/info-source-sources-of-federal-government-and-employee-information</t>
+          <t>manual:seaway_bridge</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -16400,7 +16752,11 @@
           <t>https://federalbridge.ca/transparency/info-source-sources-of-federal-government-and-employee-information</t>
         </is>
       </c>
-      <c r="Z167" t="inlineStr"/>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>https://pontsfederaux.ca/sources/cpivm</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -16413,30 +16769,20 @@
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Wek’eezhii Land and Water Board</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Office des terres et des eaux de la vallée du Mackenzie</t>
-        </is>
-      </c>
+          <t>St. Mary's River Bridge Company</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
+          <t>https://www.federalbridge.ca/transparency/info-source-sources-of-federal-government-and-employee-information/</t>
         </is>
       </c>
       <c r="J168" t="n">
-        <v>429</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
-        </is>
-      </c>
-      <c r="L168" t="n">
-        <v>429</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
@@ -16452,27 +16798,19 @@
         </is>
       </c>
       <c r="U168" t="inlineStr"/>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
+      <c r="V168" t="inlineStr"/>
       <c r="W168" t="inlineStr"/>
       <c r="X168" t="inlineStr">
         <is>
-          <t>url:https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
+          <t>url:https://federalbridge.ca/transparency/info-source-sources-of-federal-government-and-employee-information</t>
         </is>
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
-        </is>
-      </c>
+          <t>https://federalbridge.ca/transparency/info-source-sources-of-federal-government-and-employee-information</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -16485,20 +16823,30 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Women and Gender Equality</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr"/>
+          <t>Wek’eezhii Land and Water Board</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Office des terres et des eaux de la vallée du Mackenzie</t>
+        </is>
+      </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/en/women-gender-equality/transparency/annual-report-parliament-access-information-privacy/info-source-2023-2024.html</t>
+          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
         </is>
       </c>
       <c r="J169" t="n">
-        <v>200</v>
-      </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
+        <v>429</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>429</v>
+      </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr"/>
@@ -16514,19 +16862,27 @@
         </is>
       </c>
       <c r="U169" t="inlineStr"/>
-      <c r="V169" t="inlineStr"/>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W169" t="inlineStr"/>
       <c r="X169" t="inlineStr">
         <is>
-          <t>url:https://canada.ca/femmes-egalite-genres/transparence/rapport-annuel-parlement-acces-information-protection-renseignements-personnels/info-source-2023-2024.html</t>
+          <t>url:https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>https://canada.ca/women-gender-equality/transparency/annual-report-parliament-access-information-privacy/info-source-2023-2024.html</t>
-        </is>
-      </c>
-      <c r="Z169" t="inlineStr"/>
+          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -16539,20 +16895,30 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Yukon Environmental Socio-Economic Assessment Board</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr"/>
+          <t>Women and Gender Equality</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Femmes et de l’Ĕgalité des genres</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>http://www.yesab.ca/wp-content/uploads/2019/05/2019-InfoSource-Chapter.pdf</t>
+          <t>https://www.canada.ca/en/women-gender-equality/transparency/annual-report-parliament-access-information-privacy/info-source-2023-2024.html</t>
         </is>
       </c>
       <c r="J170" t="n">
         <v>200</v>
       </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://www.canada.ca/fr/femmes-egalite-genres/transparence/rapport-annuel-parlement-acces-information-protection-renseignements-personnels/info-source-2023-2024.html</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>200</v>
+      </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
@@ -16568,19 +16934,27 @@
         </is>
       </c>
       <c r="U170" t="inlineStr"/>
-      <c r="V170" t="inlineStr"/>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="W170" t="inlineStr"/>
       <c r="X170" t="inlineStr">
         <is>
-          <t>url:https://yesab.ca/wp-content/uploads/2019/05/2019-InfoSource-Chapter.pdf</t>
+          <t>manual:wage</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>https://yesab.ca/wp-content/uploads/2019/05/2019-InfoSource-Chapter.pdf</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr"/>
+          <t>https://canada.ca/women-gender-equality/transparency/annual-report-parliament-access-information-privacy/info-source-2023-2024.html</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>https://canada.ca/femmes-egalite-genres/transparence/rapport-annuel-parlement-acces-information-protection-renseignements-personnels/info-source-2023-2024.html</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -16591,22 +16965,22 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Agence Parcs Canada</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>http://www.pc.gc.ca/fr/agence-agency/dp-pd/infosource</t>
-        </is>
-      </c>
-      <c r="L171" t="n">
-        <v>200</v>
-      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Yukon Environmental Socio-Economic Assessment Board</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>http://www.yesab.ca/wp-content/uploads/2019/05/2019-InfoSource-Chapter.pdf</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>200</v>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
@@ -16616,25 +16990,25 @@
       <c r="Q171" t="inlineStr"/>
       <c r="R171" t="inlineStr"/>
       <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr"/>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>unmatched</t>
+        </is>
+      </c>
       <c r="U171" t="inlineStr"/>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
+      <c r="V171" t="inlineStr"/>
       <c r="W171" t="inlineStr"/>
       <c r="X171" t="inlineStr">
         <is>
-          <t>url:https://pc.gc.ca/agence-agency/dp-pd/infosource</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr"/>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>https://pc.gc.ca/agence-agency/dp-pd/infosource</t>
-        </is>
-      </c>
+          <t>url:https://yesab.ca/wp-content/uploads/2019/05/2019-InfoSource-Chapter.pdf</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>https://yesab.ca/wp-content/uploads/2019/05/2019-InfoSource-Chapter.pdf</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -16763,7 +17137,7 @@
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>http://www.oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-1-fra.aspx</t>
+          <t>https://www.oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-2-fra.aspx</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -16788,13 +17162,13 @@
       <c r="W174" t="inlineStr"/>
       <c r="X174" t="inlineStr">
         <is>
-          <t>url:https://oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-1-fra.aspx</t>
+          <t>url:https://oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-2-fra.aspx</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>https://oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-1-fra.aspx</t>
+          <t>https://oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-2-fra.aspx</t>
         </is>
       </c>
     </row>
@@ -16810,14 +17184,14 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bureau de l’enquêteur correctionnel</t>
+          <t>Caisse d’indemnisation pour les accidents ferroviaires impliquant des marchandises désignées</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://www.oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-2-fra.aspx</t>
+          <t>https://fraidg.gc.ca/fr/info-source/</t>
         </is>
       </c>
       <c r="L175" t="n">
@@ -16842,13 +17216,13 @@
       <c r="W175" t="inlineStr"/>
       <c r="X175" t="inlineStr">
         <is>
-          <t>url:https://oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-2-fra.aspx</t>
+          <t>url:https://fraidg.gc.ca/info-source</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>https://oci-bec.gc.ca/cnt/disc-div/atip-aiprp/infosource/infosource2018-2-fra.aspx</t>
+          <t>https://fraidg.gc.ca/info-source</t>
         </is>
       </c>
     </row>
@@ -16864,18 +17238,18 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Caisse d’indemnisation pour les accidents ferroviaires impliquant des marchandises désignées</t>
+          <t>Comité externe d’examen de la Gendarmerie royale du Canada</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://fraidg.gc.ca/fr/info-source/</t>
+          <t>https://www.canada.ca/fr/comite-externe-examen-grc/organisation/transparence/acces-information-protection-renseignements-personnels/info-source-sources-renseignements-gouvernement-federal-fonctionnaires-federaux.html</t>
         </is>
       </c>
       <c r="L176" t="n">
-        <v>404</v>
+        <v>200</v>
       </c>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
@@ -16896,13 +17270,13 @@
       <c r="W176" t="inlineStr"/>
       <c r="X176" t="inlineStr">
         <is>
-          <t>url:https://fraidg.gc.ca/info-source</t>
+          <t>url:https://canada.ca/rcmp-external-review-committee/corporate/transparency/access-information-privacy/info-source-sources-federal-government-employee-information.html</t>
         </is>
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>https://fraidg.gc.ca/info-source</t>
+          <t>https://canada.ca/comite-externe-examen-grc/organisation/transparence/acces-information-protection-renseignements-personnels/info-source-sources-renseignements-gouvernement-federal-fonctionnaires-federaux.html</t>
         </is>
       </c>
     </row>
@@ -16918,19 +17292,17 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Canada Eldor Inc.</t>
+          <t>Commission de témoignage et de réconciliation du Canada</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://www.cdev.gc.ca/fr/info-source-2/canada-eldor-inc/</t>
-        </is>
-      </c>
-      <c r="L177" t="n">
-        <v>200</v>
-      </c>
+          <t>http://www.infosource.gc.ca/inst/1678/1678-fedemp00-fra.asp</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
@@ -16950,13 +17322,13 @@
       <c r="W177" t="inlineStr"/>
       <c r="X177" t="inlineStr">
         <is>
-          <t>url:https://cdev.gc.ca/info-source-2/canada-eldor-inc</t>
+          <t>url:https://infosource.gc.ca/inst/1678/1678-fedemp00-fra.asp</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>https://cdev.gc.ca/info-source-2/canada-eldor-inc</t>
+          <t>https://infosource.gc.ca/inst/1678/1678-fedemp00-fra.asp</t>
         </is>
       </c>
     </row>
@@ -16972,19 +17344,17 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Centre national des Arts</t>
+          <t>Fiducie du Canada pour l’habitation</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>http://nac-cna.ca/fr/legal/infosource</t>
-        </is>
-      </c>
-      <c r="L178" t="n">
-        <v>200</v>
-      </c>
+          <t>http://www.infosource.gc.ca/inst/1608/1608-fedemp00-fra.asp</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
@@ -17004,13 +17374,13 @@
       <c r="W178" t="inlineStr"/>
       <c r="X178" t="inlineStr">
         <is>
-          <t>url:https://nac-cna.ca/legal/infosource</t>
+          <t>url:https://infosource.gc.ca/inst/1608/1608-fedemp00-fra.asp</t>
         </is>
       </c>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>https://nac-cna.ca/legal/infosource</t>
+          <t>https://infosource.gc.ca/inst/1608/1608-fedemp00-fra.asp</t>
         </is>
       </c>
     </row>
@@ -17026,18 +17396,18 @@
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Comité de surveillance des activités de renseignement de sécurité</t>
+          <t>Ingenium – Musées des sciences et de l’innovation du Canada</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>http://www.sirc-csars.gc.ca/prddpr/index-fra.html</t>
+          <t>https://ingeniumcanada.org/sites/default/files/2022-01/Ingenium-InfoSources-2021-french.pdf</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
@@ -17058,13 +17428,13 @@
       <c r="W179" t="inlineStr"/>
       <c r="X179" t="inlineStr">
         <is>
-          <t>url:https://sirc-csars.gc.ca/prddpr/index-fra.html</t>
+          <t>url:https://ingeniumcanada.org/sites/default/files/2022-01/Ingenium-InfoSources-2021-french.pdf</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>https://sirc-csars.gc.ca/prddpr/index-fra.html</t>
+          <t>https://ingeniumcanada.org/sites/default/files/2022-01/Ingenium-InfoSources-2021-french.pdf</t>
         </is>
       </c>
     </row>
@@ -17080,14 +17450,14 @@
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Comité externe d’examen de la Gendarmerie royale du Canada</t>
+          <t>Musée canadien de l’histoire et Musée canadien de la guerre</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/fr/comite-externe-examen-grc/organisation/transparence/acces-information-protection-renseignements-personnels/info-source-sources-renseignements-gouvernement-federal-fonctionnaires-federaux.html</t>
+          <t>https://www.museedelhistoire.ca/a-propos/a-propos-de-la-societe/rapports-de-la-societe/acces-information-protection-renseignements-personnels/?_ga=2.133904717.2113690776.1628609136-1447206126.1612812778#info-source</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -17112,13 +17482,13 @@
       <c r="W180" t="inlineStr"/>
       <c r="X180" t="inlineStr">
         <is>
-          <t>url:https://canada.ca/rcmp-external-review-committee/corporate/transparency/access-information-privacy/info-source-sources-federal-government-employee-information.html</t>
+          <t>url:https://museedelhistoire.ca/a-propos/a-propos-de-la-societe/rapports-de-la-societe/acces-information-protection-renseignements-personnels?_ga=2.133904717.2113690776.1628609136-1447206126.1612812778</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr"/>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>https://canada.ca/comite-externe-examen-grc/organisation/transparence/acces-information-protection-renseignements-personnels/info-source-sources-renseignements-gouvernement-federal-fonctionnaires-federaux.html</t>
+          <t>https://museedelhistoire.ca/a-propos/a-propos-de-la-societe/rapports-de-la-societe/acces-information-protection-renseignements-personnels?_ga=2.133904717.2113690776.1628609136-1447206126.1612812778</t>
         </is>
       </c>
     </row>
@@ -17134,17 +17504,19 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Commission de témoignage et de réconciliation du Canada</t>
+          <t>Office Gwich’in d’aménagement territorial</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>http://www.infosource.gc.ca/inst/1678/1678-fedemp00-fra.asp</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr"/>
+          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-amenagement-territorial.html</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>200</v>
+      </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
@@ -17164,13 +17536,13 @@
       <c r="W181" t="inlineStr"/>
       <c r="X181" t="inlineStr">
         <is>
-          <t>url:https://infosource.gc.ca/inst/1678/1678-fedemp00-fra.asp</t>
+          <t>url:https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-amenagement-territorial.html</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr"/>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>https://infosource.gc.ca/inst/1678/1678-fedemp00-fra.asp</t>
+          <t>https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-amenagement-territorial.html</t>
         </is>
       </c>
     </row>
@@ -17186,18 +17558,18 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Commission des traités de la Colombie Britannique</t>
+          <t>Office des terres et des eaux du Wek’èezhìi</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/commission-traites-colombie-britannique.html</t>
+          <t>https://wlwb.ca/our-board/access-information-requests-2</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>200</v>
+        <v>429</v>
       </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
@@ -17218,13 +17590,13 @@
       <c r="W182" t="inlineStr"/>
       <c r="X182" t="inlineStr">
         <is>
-          <t>url:https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/commission-traites-colombie-britannique.html</t>
+          <t>url:https://wlwb.ca/our-board/access-information-requests-2</t>
         </is>
       </c>
       <c r="Y182" t="inlineStr"/>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/commission-traites-colombie-britannique.html</t>
+          <t>https://wlwb.ca/our-board/access-information-requests-2</t>
         </is>
       </c>
     </row>
@@ -17240,18 +17612,18 @@
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Construction de Défense Canada</t>
+          <t>Office d’aménagement territorial du Sahtu</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://www.dcc-cdc.gc.ca/documents/reports/Info_Source_F.pdf</t>
+          <t>https://sahtulanduseplan.org/sites/default/files/sahtu_land_use_planning_board-fr.pdf</t>
         </is>
       </c>
       <c r="L183" t="n">
-        <v>200</v>
+        <v>429</v>
       </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
@@ -17272,13 +17644,13 @@
       <c r="W183" t="inlineStr"/>
       <c r="X183" t="inlineStr">
         <is>
-          <t>url:https://dcc-cdc.gc.ca/documents/reports/Info_Source_F.pdf</t>
+          <t>url:https://sahtulanduseplan.org/sites/default/files/sahtu_land_use_planning_board-fr.pdf</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>https://dcc-cdc.gc.ca/documents/reports/Info_Source_F.pdf</t>
+          <t>https://sahtulanduseplan.org/sites/default/files/sahtu_land_use_planning_board-fr.pdf</t>
         </is>
       </c>
     </row>
@@ -17294,14 +17666,14 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Corporation du Pont international de la Voie maritime, Limitée</t>
+          <t>Office d’évaluation environnementale et socioéconomique du Yukon</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://www.pontsfederaux.ca/sources/cpivm/</t>
+          <t>http://www.yesab.ca/about-yesab/demandes-de-communication-traitees/</t>
         </is>
       </c>
       <c r="L184" t="n">
@@ -17326,13 +17698,13 @@
       <c r="W184" t="inlineStr"/>
       <c r="X184" t="inlineStr">
         <is>
-          <t>url:https://pontsfederaux.ca/sources/cpivm</t>
+          <t>url:https://yesab.ca/about-yesab/demandes-de-communication-traitees</t>
         </is>
       </c>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>https://pontsfederaux.ca/sources/cpivm</t>
+          <t>https://yesab.ca/about-yesab/demandes-de-communication-traitees</t>
         </is>
       </c>
     </row>
@@ -17348,14 +17720,14 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Femmes et de l’Ĕgalité des genres</t>
+          <t>Revera Inc.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>https://www.canada.ca/fr/femmes-egalite-genres/transparence/rapport-annuel-parlement-acces-information-protection-renseignements-personnels/info-source-2023-2024.html</t>
+          <t>https://www.investpsp.com/fr/confidentialite/</t>
         </is>
       </c>
       <c r="L185" t="n">
@@ -17380,13 +17752,13 @@
       <c r="W185" t="inlineStr"/>
       <c r="X185" t="inlineStr">
         <is>
-          <t>url:https://canada.ca/women-gender-equality/transparency/annual-report-parliament-access-information-privacy/info-source-2023-2024.html</t>
+          <t>url:https://investpsp.com/confidentialite</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>https://canada.ca/femmes-egalite-genres/transparence/rapport-annuel-parlement-acces-information-protection-renseignements-personnels/info-source-2023-2024.html</t>
+          <t>https://investpsp.com/confidentialite</t>
         </is>
       </c>
     </row>
@@ -17402,17 +17774,19 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Fiducie du Canada pour l’habitation</t>
+          <t>Société du pont de la rivière Ste Marie</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>http://www.infosource.gc.ca/inst/1608/1608-fedemp00-fra.asp</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr"/>
+          <t>https://www.pontsfederaux.ca/sources/smrbc/</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>200</v>
+      </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
@@ -17432,1035 +17806,13 @@
       <c r="W186" t="inlineStr"/>
       <c r="X186" t="inlineStr">
         <is>
-          <t>url:https://infosource.gc.ca/inst/1608/1608-fedemp00-fra.asp</t>
+          <t>url:https://pontsfederaux.ca/sources/smrbc</t>
         </is>
       </c>
       <c r="Y186" t="inlineStr"/>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>https://infosource.gc.ca/inst/1608/1608-fedemp00-fra.asp</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr"/>
-      <c r="B187" t="b">
-        <v>0</v>
-      </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Infrastructure Canada</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr"/>
-      <c r="J187" t="inlineStr"/>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>https://www.infrastructure.gc.ca/infosource/infosource-fra.html</t>
-        </is>
-      </c>
-      <c r="L187" t="n">
-        <v>200</v>
-      </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr"/>
-      <c r="S187" t="inlineStr"/>
-      <c r="T187" t="inlineStr"/>
-      <c r="U187" t="inlineStr"/>
-      <c r="V187" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr"/>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>url:https://infrastructure.gc.ca/infosource/infosource-fra.html</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr"/>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>https://infrastructure.gc.ca/infosource/infosource-fra.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr"/>
-      <c r="B188" t="b">
-        <v>0</v>
-      </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Ingenium – Musées des sciences et de l’innovation du Canada</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>https://ingeniumcanada.org/sites/default/files/2022-01/Ingenium-InfoSources-2021-french.pdf</t>
-        </is>
-      </c>
-      <c r="L188" t="n">
-        <v>403</v>
-      </c>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
-      <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
-      <c r="U188" t="inlineStr"/>
-      <c r="V188" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr"/>
-      <c r="X188" t="inlineStr">
-        <is>
-          <t>url:https://ingeniumcanada.org/sites/default/files/2022-01/Ingenium-InfoSources-2021-french.pdf</t>
-        </is>
-      </c>
-      <c r="Y188" t="inlineStr"/>
-      <c r="Z188" t="inlineStr">
-        <is>
-          <t>https://ingeniumcanada.org/sites/default/files/2022-01/Ingenium-InfoSources-2021-french.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr"/>
-      <c r="B189" t="b">
-        <v>0</v>
-      </c>
-      <c r="C189" t="inlineStr"/>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Musée canadien de l’histoire et Musée canadien de la guerre</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr"/>
-      <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>https://www.museedelhistoire.ca/a-propos/a-propos-de-la-societe/rapports-de-la-societe/acces-information-protection-renseignements-personnels/?_ga=2.133904717.2113690776.1628609136-1447206126.1612812778#info-source</t>
-        </is>
-      </c>
-      <c r="L189" t="n">
-        <v>200</v>
-      </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr"/>
-      <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr"/>
-      <c r="V189" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr"/>
-      <c r="X189" t="inlineStr">
-        <is>
-          <t>url:https://museedelhistoire.ca/a-propos/a-propos-de-la-societe/rapports-de-la-societe/acces-information-protection-renseignements-personnels?_ga=2.133904717.2113690776.1628609136-1447206126.1612812778</t>
-        </is>
-      </c>
-      <c r="Y189" t="inlineStr"/>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>https://museedelhistoire.ca/a-propos/a-propos-de-la-societe/rapports-de-la-societe/acces-information-protection-renseignements-personnels?_ga=2.133904717.2113690776.1628609136-1447206126.1612812778</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr"/>
-      <c r="B190" t="b">
-        <v>0</v>
-      </c>
-      <c r="C190" t="inlineStr"/>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Office Canada – Nouvelle-Écosse des hydrocarbures extracôtiers</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>https://www.ocnehe.ca/sites/default/files/resource/infosource_self_publishing_french.pdf</t>
-        </is>
-      </c>
-      <c r="L190" t="n">
-        <v>200</v>
-      </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
-      <c r="V190" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr"/>
-      <c r="X190" t="inlineStr">
-        <is>
-          <t>url:https://ocnehe.ca/sites/default/files/resource/infosource_self_publishing_french.pdf</t>
-        </is>
-      </c>
-      <c r="Y190" t="inlineStr"/>
-      <c r="Z190" t="inlineStr">
-        <is>
-          <t>https://ocnehe.ca/sites/default/files/resource/infosource_self_publishing_french.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr"/>
-      <c r="B191" t="b">
-        <v>0</v>
-      </c>
-      <c r="C191" t="inlineStr"/>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Office Gwich’in des terres et des eaux</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-terres-eaux.html</t>
-        </is>
-      </c>
-      <c r="L191" t="n">
-        <v>200</v>
-      </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
-      <c r="U191" t="inlineStr"/>
-      <c r="V191" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr"/>
-      <c r="X191" t="inlineStr">
-        <is>
-          <t>url:https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-terres-eaux.html</t>
-        </is>
-      </c>
-      <c r="Y191" t="inlineStr"/>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-terres-eaux.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr"/>
-      <c r="B192" t="b">
-        <v>0</v>
-      </c>
-      <c r="C192" t="inlineStr"/>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Office Gwich’in d’aménagement territorial</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>https://www.canada.ca/fr/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-amenagement-territorial.html</t>
-        </is>
-      </c>
-      <c r="L192" t="n">
-        <v>200</v>
-      </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
-      <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
-      <c r="U192" t="inlineStr"/>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr"/>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>url:https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-amenagement-territorial.html</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr"/>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>https://canada.ca/secretariat-conseil-tresor/services/acces-information-protection-reseignements-personnels/acces-information/renseignements-programmes-fonds-renseignements/office-gwichin-amenagement-territorial.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr"/>
-      <c r="B193" t="b">
-        <v>0</v>
-      </c>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Office des eaux du Nunavut</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>http://www.nwb-oen.ca/fr/content/transparence</t>
-        </is>
-      </c>
-      <c r="L193" t="n">
-        <v>200</v>
-      </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q193" t="inlineStr"/>
-      <c r="R193" t="inlineStr"/>
-      <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
-      <c r="U193" t="inlineStr"/>
-      <c r="V193" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr"/>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>url:https://nwb-oen.ca/content/transparence</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr"/>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>https://nwb-oen.ca/content/transparence</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr"/>
-      <c r="B194" t="b">
-        <v>0</v>
-      </c>
-      <c r="C194" t="inlineStr"/>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Office des terres et des eaux du Sahtu</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr"/>
-      <c r="J194" t="inlineStr"/>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf?_gl=1*1qsdw3z*_ga*ODE3NjYzOTEwLjE2NjYyMDQwNTQ.*_ga_1YN4RQ50MS*MTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..*_ga_DM4CTC801Y*MTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..*_ga_WH73GNZLKK*MTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..*_ga_FFVRERZXBW*MTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..</t>
-        </is>
-      </c>
-      <c r="L194" t="n">
-        <v>429</v>
-      </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr"/>
-      <c r="S194" t="inlineStr"/>
-      <c r="T194" t="inlineStr"/>
-      <c r="U194" t="inlineStr"/>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr"/>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>url:https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf?_gl=1%2A1qsdw3z%2A_ga%2AODE3NjYzOTEwLjE2NjYyMDQwNTQ.%2A_ga_1YN4RQ50MS%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_DM4CTC801Y%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_WH73GNZLKK%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_FFVRERZXBW%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr"/>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>https://wlwb.ca/sites/default/files/mvlwb_-_info_source_-_may_14_19.pdf?_gl=1%2A1qsdw3z%2A_ga%2AODE3NjYzOTEwLjE2NjYyMDQwNTQ.%2A_ga_1YN4RQ50MS%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_DM4CTC801Y%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_WH73GNZLKK%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..%2A_ga_FFVRERZXBW%2AMTY2NjIwNDA1My4xLjEuMTY2NjIwNDQ1Ny4wLjAuMA..</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr"/>
-      <c r="B195" t="b">
-        <v>0</v>
-      </c>
-      <c r="C195" t="inlineStr"/>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Office des terres et des eaux du Wek’èezhìi</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>https://wlwb.ca/our-board/access-information-requests-2</t>
-        </is>
-      </c>
-      <c r="L195" t="n">
-        <v>429</v>
-      </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
-      <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
-      <c r="V195" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W195" t="inlineStr"/>
-      <c r="X195" t="inlineStr">
-        <is>
-          <t>url:https://wlwb.ca/our-board/access-information-requests-2</t>
-        </is>
-      </c>
-      <c r="Y195" t="inlineStr"/>
-      <c r="Z195" t="inlineStr">
-        <is>
-          <t>https://wlwb.ca/our-board/access-information-requests-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr"/>
-      <c r="B196" t="b">
-        <v>0</v>
-      </c>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Office d’aménagement territorial du Sahtu</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>https://sahtulanduseplan.org/sites/default/files/sahtu_land_use_planning_board-fr.pdf</t>
-        </is>
-      </c>
-      <c r="L196" t="n">
-        <v>429</v>
-      </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q196" t="inlineStr"/>
-      <c r="R196" t="inlineStr"/>
-      <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr"/>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>url:https://sahtulanduseplan.org/sites/default/files/sahtu_land_use_planning_board-fr.pdf</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr"/>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>https://sahtulanduseplan.org/sites/default/files/sahtu_land_use_planning_board-fr.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr"/>
-      <c r="B197" t="b">
-        <v>0</v>
-      </c>
-      <c r="C197" t="inlineStr"/>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Office d’évaluation environnementale et socioéconomique du Yukon</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>http://www.yesab.ca/about-yesab/demandes-de-communication-traitees/</t>
-        </is>
-      </c>
-      <c r="L197" t="n">
-        <v>200</v>
-      </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="inlineStr"/>
-      <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
-      <c r="U197" t="inlineStr"/>
-      <c r="V197" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr"/>
-      <c r="X197" t="inlineStr">
-        <is>
-          <t>url:https://yesab.ca/about-yesab/demandes-de-communication-traitees</t>
-        </is>
-      </c>
-      <c r="Y197" t="inlineStr"/>
-      <c r="Z197" t="inlineStr">
-        <is>
-          <t>https://yesab.ca/about-yesab/demandes-de-communication-traitees</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr"/>
-      <c r="B198" t="b">
-        <v>0</v>
-      </c>
-      <c r="C198" t="inlineStr"/>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Office national de l’énergie</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>https://www.cer-rec.gc.ca/fr/regie/gouvernement-ouvert/transparence/demandes-acces-information-completees/info-source.html</t>
-        </is>
-      </c>
-      <c r="L198" t="n">
-        <v>200</v>
-      </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
-      <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr"/>
-      <c r="U198" t="inlineStr"/>
-      <c r="V198" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W198" t="inlineStr"/>
-      <c r="X198" t="inlineStr">
-        <is>
-          <t>url:https://cer-rec.gc.ca/regie/gouvernement-ouvert/transparence/demandes-acces-information-completees/info-source.html</t>
-        </is>
-      </c>
-      <c r="Y198" t="inlineStr"/>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>https://cer-rec.gc.ca/regie/gouvernement-ouvert/transparence/demandes-acces-information-completees/info-source.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr"/>
-      <c r="B199" t="b">
-        <v>0</v>
-      </c>
-      <c r="C199" t="inlineStr"/>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>Office national du film du Canada</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>http://onf-nfb.gc.ca/fr/a-propos-de-lonf/publications/info-source/</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="inlineStr"/>
-      <c r="S199" t="inlineStr"/>
-      <c r="T199" t="inlineStr"/>
-      <c r="U199" t="inlineStr"/>
-      <c r="V199" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W199" t="inlineStr"/>
-      <c r="X199" t="inlineStr">
-        <is>
-          <t>url:https://onf-nfb.gc.ca/a-propos-de-lonf/publications/info-source</t>
-        </is>
-      </c>
-      <c r="Y199" t="inlineStr"/>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>https://onf-nfb.gc.ca/a-propos-de-lonf/publications/info-source</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr"/>
-      <c r="B200" t="b">
-        <v>0</v>
-      </c>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Port de Vancouver</t>
-        </is>
-      </c>
-      <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>https://view.officeapps.live.com/op/view.aspx?src=https%3A%2F%2Fwww.portvancouver.com%2Fwp-content%2Fuploads%2F2015%2F07%2F2017-Sources-de-renseignements-du-gouvernement-f%25C3%25A9d%25C3%25A9ral.docx&amp;wdOrigin=BROWSELINK</t>
-        </is>
-      </c>
-      <c r="L200" t="n">
-        <v>200</v>
-      </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
-      <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
-      <c r="U200" t="inlineStr"/>
-      <c r="V200" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr"/>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>url:https://view.officeapps.live.com/op/view.aspx?src=https%3A%2F%2Fwww.portvancouver.com%2Fwp-content%2Fuploads%2F2015%2F07%2F2017-Sources-de-renseignements-du-gouvernement-f%25C3%25A9d%25C3%25A9ral.docx&amp;wdOrigin=BROWSELINK</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr"/>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>https://view.officeapps.live.com/op/view.aspx?src=https%3A%2F%2Fwww.portvancouver.com%2Fwp-content%2Fuploads%2F2015%2F07%2F2017-Sources-de-renseignements-du-gouvernement-f%25C3%25A9d%25C3%25A9ral.docx&amp;wdOrigin=BROWSELINK</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr"/>
-      <c r="B201" t="b">
-        <v>0</v>
-      </c>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Postes Canada</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>https://www.canadapost-postescanada.ca/scp/fr/notre-entreprise/a-notre-sujet/transparence-et-confiance/centre-de-protection-de-la-vie-privee/info-source/introduction-a-info-source.page</t>
-        </is>
-      </c>
-      <c r="L201" t="n">
-        <v>200</v>
-      </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="inlineStr"/>
-      <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr"/>
-      <c r="U201" t="inlineStr"/>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr"/>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>url:https://canadapost-postescanada.ca/scp/notre-entreprise/a-notre-sujet/transparence-et-confiance/centre-de-protection-de-la-vie-privee/info-source/introduction-a-info-source.page</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr"/>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>https://canadapost-postescanada.ca/scp/notre-entreprise/a-notre-sujet/transparence-et-confiance/centre-de-protection-de-la-vie-privee/info-source/introduction-a-info-source.page</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr"/>
-      <c r="B202" t="b">
-        <v>0</v>
-      </c>
-      <c r="C202" t="inlineStr"/>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Revera Inc.</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>https://www.investpsp.com/fr/confidentialite/</t>
-        </is>
-      </c>
-      <c r="L202" t="n">
-        <v>200</v>
-      </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="inlineStr"/>
-      <c r="S202" t="inlineStr"/>
-      <c r="T202" t="inlineStr"/>
-      <c r="U202" t="inlineStr"/>
-      <c r="V202" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W202" t="inlineStr"/>
-      <c r="X202" t="inlineStr">
-        <is>
-          <t>url:https://investpsp.com/confidentialite</t>
-        </is>
-      </c>
-      <c r="Y202" t="inlineStr"/>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>https://investpsp.com/confidentialite</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr"/>
-      <c r="B203" t="b">
-        <v>0</v>
-      </c>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Société de gestion Canada Hibernia</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>https://www.cdev.gc.ca/fr/info-source-2/societe-de-gestion-canada-hibernia/</t>
-        </is>
-      </c>
-      <c r="L203" t="n">
-        <v>200</v>
-      </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr"/>
-      <c r="T203" t="inlineStr"/>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr"/>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>url:https://cdev.gc.ca/info-source-2/societe-de-gestion-canada-hibernia</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr"/>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>https://cdev.gc.ca/info-source-2/societe-de-gestion-canada-hibernia</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr"/>
-      <c r="B204" t="b">
-        <v>0</v>
-      </c>
-      <c r="C204" t="inlineStr"/>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Société du pont de la rivière Ste Marie</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>https://www.pontsfederaux.ca/sources/smrbc/</t>
-        </is>
-      </c>
-      <c r="L204" t="n">
-        <v>200</v>
-      </c>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q204" t="inlineStr"/>
-      <c r="R204" t="inlineStr"/>
-      <c r="S204" t="inlineStr"/>
-      <c r="T204" t="inlineStr"/>
-      <c r="U204" t="inlineStr"/>
-      <c r="V204" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W204" t="inlineStr"/>
-      <c r="X204" t="inlineStr">
-        <is>
-          <t>url:https://pontsfederaux.ca/sources/smrbc</t>
-        </is>
-      </c>
-      <c r="Y204" t="inlineStr"/>
-      <c r="Z204" t="inlineStr">
-        <is>
           <t>https://pontsfederaux.ca/sources/smrbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr"/>
-      <c r="B205" t="b">
-        <v>0</v>
-      </c>
-      <c r="C205" t="inlineStr"/>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Technologies du développement durable du Canada</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr"/>
-      <c r="J205" t="inlineStr"/>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>https://www.sdtc.ca/fr/a-propos/responsabilite/info-source/</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr"/>
-      <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr"/>
-      <c r="U205" t="inlineStr"/>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>unmatched</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr"/>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>url:https://sdtc.ca/a-propos/responsabilite/info-source</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr"/>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>https://sdtc.ca/a-propos/responsabilite/info-source</t>
         </is>
       </c>
     </row>
